--- a/SGC-CKN/Excel/59734182-34dd-473c-aab5-05a0d60187f5_Lô_đất_ký_hiệu_CT-02_P7-130_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/59734182-34dd-473c-aab5-05a0d60187f5_Lô_đất_ký_hiệu_CT-02_P7-130_D800_17-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -194,9 +194,6 @@
   <si>
     <t xml:space="preserve">06:10
 17/03/2026</t>
-  </si>
-  <si>
-    <t>Có ghi chú cao độ khác 45,08 tại cuối lớp</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1486,16 +1483,16 @@
         <v>-39</v>
       </c>
       <c r="G19" s="31">
-        <v>-43</v>
+        <v>-43.57</v>
       </c>
       <c r="H19" s="31">
         <v>1.15</v>
       </c>
       <c r="I19" s="31">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="J19" s="24">
-        <v>3.48</v>
+        <v>3.97</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>53</v>
@@ -1518,27 +1515,27 @@
         <v>56</v>
       </c>
       <c r="F20" s="34">
-        <v>-43</v>
+        <v>-43.57</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.57</v>
+        <v>-45.08</v>
       </c>
       <c r="H20" s="34">
         <v>0.5</v>
       </c>
       <c r="I20" s="34">
-        <v>2.57</v>
-      </c>
-      <c r="J20" s="8">
-        <v>5.14</v>
+        <v>1.51</v>
+      </c>
+      <c r="J20" s="24">
+        <v>3.02</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1644,31 +1641,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1920,16 +1917,16 @@
         <v>-39</v>
       </c>
       <c r="F10" s="31">
-        <v>-43</v>
+        <v>-43.57</v>
       </c>
       <c r="G10" s="31">
         <v>1.15</v>
       </c>
       <c r="H10" s="31">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="I10" s="24">
-        <v>3.48</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1946,24 +1943,24 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-43</v>
+        <v>-43.57</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.57</v>
+        <v>-45.08</v>
       </c>
       <c r="G11" s="34">
         <v>0.5</v>
       </c>
       <c r="H11" s="34">
-        <v>2.57</v>
-      </c>
-      <c r="I11" s="8">
-        <v>5.14</v>
+        <v>1.51</v>
+      </c>
+      <c r="I11" s="24">
+        <v>3.02</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1978,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-45.57</v>
+        <v>-45.08</v>
       </c>
       <c r="G12" s="39">
         <v>10.17</v>
       </c>
       <c r="H12" s="39">
-        <v>45.57</v>
+        <v>45.08</v>
       </c>
       <c r="I12" s="39">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
     </row>
   </sheetData>
